--- a/artfynd/A 27001-2025 artfynd.xlsx
+++ b/artfynd/A 27001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127392888</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27001-2025 artfynd.xlsx
+++ b/artfynd/A 27001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127392888</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27001-2025 artfynd.xlsx
+++ b/artfynd/A 27001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127392888</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27001-2025 artfynd.xlsx
+++ b/artfynd/A 27001-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127392888</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27001-2025 artfynd.xlsx
+++ b/artfynd/A 27001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127392888</v>
+        <v>127390798</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>355776</v>
+        <v>355790</v>
       </c>
       <c r="R2" t="n">
-        <v>6584171</v>
+        <v>6584231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -784,6 +769,1605 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127392888</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ragnilrud, Ragnilrud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>355776</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6584171</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102007170</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43438</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Melitaea diamina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>355754</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6583921</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102096284</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ragnilrud, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>355750</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6583929</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101816575</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45033</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsmetallvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Adscita statices</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>355766</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584024</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102249553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ragnilrud, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>355769</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6584075</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>101998506</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>355754</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6583921</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>101753165</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>355777</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6584023</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102095605</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>355773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6584020</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101753105</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>355777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6584023</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2371013</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ragnilrud, östra ängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>355781</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6584131</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>S-Årj-0106</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2011-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2011-07-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett flertal grupper, vid angivna koordinater, 15 bladrosetter-9 blomstänglar. 6588293-1310074, 20 bladrosetter-18 blomstänglar. 6588345-1310040, 10 bladrosetter-4 blomstänglar. 6588000-1310000, 3 grupper med 70 bladrosetter-50 blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>hävdad ängsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110302112</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ragnilrud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>355784</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6584128</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96584332</v>
+      </c>
+      <c r="B14" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1,Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>355767</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6583942</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>101428143</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ragnilrud 1, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>355780</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6584033</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109616638</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ragnilrud, västra ängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>355779</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6584032</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>S-Årj-0347</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Åsa Enefalk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101815640</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ragnilrud, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>355745</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6583971</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pierre Norqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
